--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N4_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>78.39680608409169</v>
+        <v>12.7394809886649</v>
       </c>
       <c r="D2" t="n">
-        <v>80.34990588288481</v>
+        <v>13.05685970596878</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
